--- a/backtest_runs/20260410_193731/by_symbol/MIRKS/MIRKS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MIRKS/MIRKS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-10508.33999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98859.56000000001</v>
@@ -771,7 +771,7 @@
         <v>-1914.309999999995</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>104073</v>
@@ -817,7 +817,7 @@
         <v>-40.73000000000637</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>104032.27</v>
@@ -909,7 +909,7 @@
         <v>-7249.940000000005</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>96782.33</v>
@@ -1139,7 +1139,7 @@
         <v>-977.5199999999936</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>105091.25</v>
@@ -1185,7 +1185,7 @@
         <v>-2362.340000000007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>102728.91</v>
@@ -1323,7 +1323,7 @@
         <v>-1669.930000000001</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>101262.63</v>
@@ -1415,7 +1415,7 @@
         <v>-2036.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>103095.48</v>
@@ -1645,7 +1645,7 @@
         <v>-4032.269999999994</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>108308.92</v>
